--- a/ipo-analysis/companies/m-k-sons-fine-jewels-ltd/M_K_SONS_FINE_JEWELS_LTD_01_Screening.xlsx
+++ b/ipo-analysis/companies/m-k-sons-fine-jewels-ltd/M_K_SONS_FINE_JEWELS_LTD_01_Screening.xlsx
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>46022</v>
+        <v>46112</v>
       </c>
       <c r="D9" s="8" t="inlineStr"/>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Price band, lot, issue split and dates from the NSE issue page; RHP not reachable, so DRHP (May-2026) figures are used</t>
+          <t>RHP not reachable; FY24-25 and Dec-25 detail from the DRHP (May-2026), FY26 headline figures from the RHP as reproduced by IPO trackers (29-Oct-2026)</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr"/>
@@ -1307,20 +1307,18 @@
         </is>
       </c>
       <c r="C5" s="16" t="n">
-        <v>24.912</v>
+        <v>217.323</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>217.323</v>
+        <v>351.28</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>351.28</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>360.821</v>
-      </c>
+        <v>538.73</v>
+      </c>
+      <c r="F5" s="16" t="n"/>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>p. 227</t>
+          <t>p. 227; FY26 from RHP as reproduced by IPO trackers (Finology, INDmoney, Paytm Money)</t>
         </is>
       </c>
     </row>
@@ -1331,17 +1329,13 @@
         </is>
       </c>
       <c r="C6" s="16" t="n">
-        <v>0.018</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="E6" s="16" t="n">
         <v>0.036</v>
       </c>
-      <c r="F6" s="16" t="n">
-        <v>0.024</v>
-      </c>
+      <c r="E6" s="16" t="n"/>
+      <c r="F6" s="16" t="n"/>
       <c r="G6" s="7" t="inlineStr">
         <is>
           <t>p. 227</t>
@@ -1355,17 +1349,13 @@
         </is>
       </c>
       <c r="C7" s="16" t="n">
-        <v>1.725</v>
+        <v>10.832</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>10.832</v>
-      </c>
-      <c r="E7" s="16" t="n">
         <v>32.026</v>
       </c>
-      <c r="F7" s="16" t="n">
-        <v>39.946</v>
-      </c>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
       <c r="G7" s="7" t="inlineStr">
         <is>
           <t>p. 227</t>
@@ -1379,17 +1369,13 @@
         </is>
       </c>
       <c r="C8" s="16" t="n">
-        <v>0.483</v>
+        <v>2.789</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>2.789</v>
-      </c>
-      <c r="E8" s="16" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="F8" s="16" t="n">
-        <v>11</v>
-      </c>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
       <c r="G8" s="7" t="inlineStr">
         <is>
           <t>p. 227</t>
@@ -1403,17 +1389,13 @@
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>-0.097</v>
+        <v>-0.122</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>-0.122</v>
-      </c>
-      <c r="E9" s="16" t="n">
         <v>0.213</v>
       </c>
-      <c r="F9" s="16" t="n">
-        <v>-0.219</v>
-      </c>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="16" t="n"/>
       <c r="G9" s="7" t="inlineStr">
         <is>
           <t>p. 227</t>
@@ -1427,20 +1409,18 @@
         </is>
       </c>
       <c r="C10" s="16" t="n">
-        <v>1.339</v>
+        <v>8.164999999999999</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>8.164999999999999</v>
+        <v>23.262</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>23.262</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>29.165</v>
-      </c>
+        <v>51.79</v>
+      </c>
+      <c r="F10" s="16" t="n"/>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>p. 227</t>
+          <t>p. 227; FY26 from RHP as reproduced by IPO trackers (Finology, INDmoney, Paytm Money)</t>
         </is>
       </c>
     </row>
@@ -1451,20 +1431,18 @@
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>-4.947</v>
+        <v>-23.557</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>-23.557</v>
+        <v>-9.531000000000001</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-9.531000000000001</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>18.006</v>
-      </c>
+        <v>15.4</v>
+      </c>
+      <c r="F11" s="16" t="n"/>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>p. 228</t>
+          <t>p. 228; FY26 from RHP as reproduced by IPO trackers (Finology, INDmoney, Paytm Money)</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1458,8 @@
       <c r="D12" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
       <c r="G12" s="7" t="inlineStr">
         <is>
           <t>p. 64</t>
@@ -1499,17 +1473,13 @@
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>0.459</v>
+        <v>3.849</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>3.849</v>
-      </c>
-      <c r="E13" s="16" t="n">
         <v>21.715</v>
       </c>
-      <c r="F13" s="16" t="n">
-        <v>1.228</v>
-      </c>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
       <c r="G13" s="7" t="inlineStr">
         <is>
           <t>p. 64 (purchases from the promoter's proprietorship before its merger, a promoter-group hotel, and rent to the promoter)</t>
@@ -1523,20 +1493,18 @@
         </is>
       </c>
       <c r="C14" s="16" t="n">
-        <v>14.149</v>
+        <v>22.29</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>22.29</v>
+        <v>116.235</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>116.235</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>145.418</v>
-      </c>
+        <v>168.01</v>
+      </c>
+      <c r="F14" s="16" t="n"/>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>p. 226</t>
+          <t>p. 226; FY26 from RHP as reproduced by IPO trackers (Finology, INDmoney, Paytm Money)</t>
         </is>
       </c>
     </row>
@@ -1547,17 +1515,13 @@
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.13</v>
+        <v>0.589</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="E15" s="16" t="n">
         <v>1.21</v>
       </c>
-      <c r="F15" s="16" t="n">
-        <v>3.422</v>
-      </c>
+      <c r="E15" s="16" t="n"/>
+      <c r="F15" s="16" t="n"/>
       <c r="G15" s="7" t="inlineStr">
         <is>
           <t>p. 226</t>
@@ -1571,17 +1535,13 @@
         </is>
       </c>
       <c r="C16" s="16" t="n">
-        <v>44.812</v>
+        <v>87.48099999999999</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>87.48099999999999</v>
-      </c>
-      <c r="E16" s="16" t="n">
         <v>205.696</v>
       </c>
-      <c r="F16" s="16" t="n">
-        <v>240.592</v>
-      </c>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
       <c r="G16" s="7" t="inlineStr">
         <is>
           <t>p. 226</t>
@@ -1595,17 +1555,13 @@
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>21.644</v>
+        <v>26.055</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>26.055</v>
-      </c>
-      <c r="E17" s="16" t="n">
         <v>21.569</v>
       </c>
-      <c r="F17" s="16" t="n">
-        <v>28.609</v>
-      </c>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
       <c r="G17" s="7" t="inlineStr">
         <is>
           <t>p. 226</t>
@@ -1624,12 +1580,8 @@
       <c r="D18" s="16" t="n">
         <v>4.995</v>
       </c>
-      <c r="E18" s="16" t="n">
-        <v>4.995</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>4.995</v>
-      </c>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="16" t="n"/>
       <c r="G18" s="7" t="inlineStr">
         <is>
           <t>p. 63 (income-tax demands AY 2012-13 and 2017-18)</t>
@@ -1648,12 +1600,8 @@
       <c r="D19" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="16" t="n"/>
       <c r="G19" s="7" t="inlineStr">
         <is>
           <t>p. 226</t>
@@ -2445,7 +2393,7 @@
       </c>
       <c r="G6" s="27" t="inlineStr">
         <is>
-          <t>Operating cash flow Rs -4.95 / -23.56 / -9.53 cr FY23-25 against PAT Rs 1.34 / 8.17 / 23.26 cr as inventory rose from Rs 44.81 cr to Rs 205.70 cr; 9M FY26 CFO +Rs 18.01 cr against PAT Rs 29.17 cr. Typical for a jewellery retailer stocking new showrooms; inventory days 122 -&gt; 178 -&gt; 205 (p. 101).</t>
+          <t>Operating cash flow Rs -23.56 / -9.53 cr FY24-25 (DRHP p. 228) and +Rs 15.40 cr in FY26 (RHP via trackers) against PAT Rs 8.17 / 23.26 / 51.79 cr; one tracker reports Q1 FY27 CFO about Rs -2.84 cr (single source). Typical for a jewellery retailer stocking new showrooms; most profit is reinvested in inventory.</t>
         </is>
       </c>
     </row>
